--- a/resources/data-imports/Monsters/delusional-memories-raid-monsters.xlsx
+++ b/resources/data-imports/Monsters/delusional-memories-raid-monsters.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -400,34 +400,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -573,7 +573,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AX15"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36.71"/>
@@ -831,7 +831,7 @@
         <v>0.177493181726</v>
       </c>
       <c r="W2" s="1" t="n">
-        <v>6425925873.481</v>
+        <v>500000</v>
       </c>
       <c r="X2" s="1" t="n">
         <v>0</v>
@@ -971,7 +971,7 @@
         <v>0.199851997828024</v>
       </c>
       <c r="W3" s="1" t="n">
-        <v>8144671479.8239</v>
+        <v>693267</v>
       </c>
       <c r="X3" s="1" t="n">
         <v>0</v>
@@ -1111,7 +1111,7 @@
         <v>0.22502735399442</v>
       </c>
       <c r="W4" s="1" t="n">
-        <v>10323130832.8681</v>
+        <v>961239</v>
       </c>
       <c r="X4" s="1" t="n">
         <v>0</v>
@@ -1251,7 +1251,7 @@
         <v>0.253374049777098</v>
       </c>
       <c r="W5" s="1" t="n">
-        <v>13084263798.3008</v>
+        <v>1332790</v>
       </c>
       <c r="X5" s="1" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>0.285291578827518</v>
       </c>
       <c r="W6" s="1" t="n">
-        <v>16583918378.5642</v>
+        <v>1847960</v>
       </c>
       <c r="X6" s="1" t="n">
         <v>0</v>
@@ -1525,7 +1525,7 @@
         <v>0.321229759012421</v>
       </c>
       <c r="W7" s="1" t="n">
-        <v>21019627319.238</v>
+        <v>2562259</v>
       </c>
       <c r="X7" s="1" t="n">
         <v>0</v>
@@ -1659,7 +1659,7 @@
         <v>0.361695071755216</v>
       </c>
       <c r="W8" s="1" t="n">
-        <v>26641757548.1282</v>
+        <v>3552661</v>
       </c>
       <c r="X8" s="1" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
         <v>0.40725779994422</v>
       </c>
       <c r="W9" s="1" t="n">
-        <v>33767641760.4048</v>
+        <v>4925886</v>
       </c>
       <c r="X9" s="1" t="n">
         <v>0</v>
@@ -1936,7 +1936,7 @@
         <v>0.458560065003193</v>
       </c>
       <c r="W10" s="1" t="n">
-        <v>42799489785.8812</v>
+        <v>6829909</v>
       </c>
       <c r="X10" s="1" t="n">
         <v>0</v>
@@ -2070,7 +2070,7 @@
         <v>0.516324876391646</v>
       </c>
       <c r="W11" s="1" t="n">
-        <v>54247090718.6557</v>
+        <v>9469904</v>
       </c>
       <c r="X11" s="1" t="n">
         <v>0</v>
@@ -2207,7 +2207,7 @@
         <v>0.581366321070701</v>
       </c>
       <c r="W12" s="1" t="n">
-        <v>68756587196.7199</v>
+        <v>13130346</v>
       </c>
       <c r="X12" s="1" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>0.654601036535977</v>
       </c>
       <c r="W13" s="1" t="n">
-        <v>87146945952.5202</v>
+        <v>18205676</v>
       </c>
       <c r="X13" s="1" t="n">
         <v>0</v>
@@ -2478,7 +2478,7 @@
         <v>0.737061129108414</v>
       </c>
       <c r="W14" s="1" t="n">
-        <v>110456183159.914</v>
+        <v>25242794</v>
       </c>
       <c r="X14" s="1" t="n">
         <v>0</v>
@@ -2612,7 +2612,7 @@
         <v>0.829908719542201</v>
       </c>
       <c r="W15" s="1" t="n">
-        <v>139999953697.787</v>
+        <v>34999999</v>
       </c>
       <c r="X15" s="1" t="n">
         <v>0</v>
